--- a/forms/trg/Formulir_TRG_sbm.xlsx
+++ b/forms/trg/Formulir_TRG_sbm.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B25)</f>
+        <f>COUNTA(Anggota!B5:B26)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F25)</f>
+        <f>COUNTA(Anggota!F5:F26)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Andi Raina Ananda Herdiyana, S.E., MSc</t>
+          <t>Prof. Dr. Abdul Rahman Kadir, SE.,M.Si</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Universitas Hasanuddin</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Management Strategic</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,11 +933,19 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0009-0000-0589-5104</t>
-        </is>
-      </c>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+          <t>0000-0002-5527-6018</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6025871</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57193806364</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -954,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Fakhrul Indra Hermansyah, S.E., M.Sc</t>
+          <t>Andi Raina Ananda Herdiyana, S.E., MSc</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -969,7 +973,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Ekonomi Islam</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -978,19 +982,11 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0009-0000-6246-2954%20View%20this%20author’s%20ORCID%20profile</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>6885421</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>59232685400</t>
-        </is>
-      </c>
+          <t>0009-0000-0589-5104</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1003,12 +999,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Andi Tenri Harahap, BA (Hons), MM,</t>
+          <t>Fakhrul Indra Hermansyah, S.E., M.Sc</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1018,16 +1014,28 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Strategic &amp; Wealth Management</t>
+          <t>Ekonomi Islam</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
-      <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0009-0000-6246-2954%20View%20this%20author’s%20ORCID%20profile</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6885421</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>59232685400</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1040,12 +1048,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Rianda Ridho Hafiz Thaha, S.E., MBA</t>
+          <t>Dr. Andi Tenri Harahap, BA (Hons), MM,</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1055,28 +1063,16 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Strategic &amp; Wealth Management</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-7150-2732</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>6782331</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>58118587400</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1089,17 +1085,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Musab Iqtait</t>
+          <t>Rianda Ridho Hafiz Thaha, S.E., MBA</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>University Zarqa</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -1113,13 +1109,17 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2091-5657</t>
-        </is>
-      </c>
-      <c r="K9" s="12" t="n"/>
+          <t>0000-0002-7150-2732</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>6782331</t>
+        </is>
+      </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57201547228</t>
+          <t>58118587400</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Najmi Kamariah, SE., M.Si.</t>
+          <t>Musab Iqtait</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Info Politeknik STIA LAN Makassar</t>
+          <t>University Zarqa</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Management Strategic Sektor Publik</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1158,17 +1158,13 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-2866-6213</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>6181907</t>
-        </is>
-      </c>
+          <t>0000-0003-2091-5657</t>
+        </is>
+      </c>
+      <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57193810933</t>
+          <t>57201547228</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1183,22 +1179,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Raehana Tul Jannah, SE</t>
+          <t>Prof. Dr. Najmi Kamariah, SE., M.Si.</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Info Politeknik STIA LAN Makassar</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Ekonomi Pembangunan dan Perencanaan</t>
+          <t>Management Strategic Sektor Publik</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1207,11 +1203,19 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0009-0000-0589-5104</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
+          <t>0000-0002-2866-6213</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6181907</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>57193810933</t>
+        </is>
+      </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1224,12 +1228,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Sabbar Dahham Sabbar</t>
+          <t>Raehana Tul Jannah, SE</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1239,24 +1243,20 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Manajemen</t>
+          <t>Ekonomi Pembangunan dan Perencanaan</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>6863841</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>58155587300</t>
-        </is>
-      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>0009-0000-0589-5104</t>
+        </is>
+      </c>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Nur Rezky Amaliah</t>
+          <t>Sabbar Dahham Sabbar</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1284,20 +1284,24 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Sains Manajemen</t>
+          <t>Manajemen</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>0009-0001-5070-8299</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>6863841</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>58155587300</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1308,18 +1312,42 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="11" t="n"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Nur Rezky Amaliah</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Sains Manajemen</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>0009-0001-5070-8299</t>
+        </is>
+      </c>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="12" t="n"/>
-      <c r="M14" s="12" t="n"/>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1508,15 +1536,32 @@
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="12" t="n"/>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
